--- a/其他資料/問卷調查/二手書籍交易行為與市場需求調查(711禮卷).xlsx
+++ b/其他資料/問卷調查/二手書籍交易行為與市場需求調查(711禮卷).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10402"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a0966\Desktop\SaveMyBook\其他資料\問卷調查\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xukaijun/Desktop/SaveMyBook/其他資料/問卷調查/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FA9E8465-A631-4918-BC60-1009B4129B25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12008388-84BE-9345-9A77-4F28EE6CF6B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20100" yWindow="8745" windowWidth="28800" windowHeight="15345" xr2:uid="{37F2E017-8173-4B92-AF40-A79063FD7598}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17200" xr2:uid="{37F2E017-8173-4B92-AF40-A79063FD7598}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="104">
   <si>
     <t>https://media-asse-txc.ticketxpress.com/tw/api/Mda/Media/GetBarcode?&amp;barcode=GXzaIXAh8dtlCn4Gcykeifntu5goO0YZru7J8cHAu%2balZkvx9PQyVt2puHXaRqCzKAMYzV2rSQeNyNWQZ0lpH24PzTLrrHjuwU3NgYAjcbVY9txDiRa2zNiwGT5WrASK&amp;BarcodeType=2&amp;IsDisplayText=Y&amp;IsEncryptedBarcode=true</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -49,10 +49,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>7100016329342227</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -379,6 +375,66 @@
   <si>
     <t>https://txp.rs/viewvoucher.aspx?voucherguid=90eaeea4-ec18-4428-9177-9f7579c59a13</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>richard030509@gmail.com</t>
+  </si>
+  <si>
+    <t>tsz0405@gmail.com</t>
+  </si>
+  <si>
+    <t>mingxuelin5@gmail.com</t>
+  </si>
+  <si>
+    <t>ethan.wei2007@gmail.com</t>
+  </si>
+  <si>
+    <t>xuan070840129@gmail.com</t>
+  </si>
+  <si>
+    <t>angelliu1228@gmail.com</t>
+  </si>
+  <si>
+    <t>anna105262@gmail.com</t>
+  </si>
+  <si>
+    <t>a410085028@gmail.com</t>
+  </si>
+  <si>
+    <t>xie77033@gmail.com</t>
+  </si>
+  <si>
+    <t>pat930908@gmail.com</t>
+  </si>
+  <si>
+    <t>sayanoyuk1i@gmail.com</t>
+  </si>
+  <si>
+    <t>carl6125@yahoo.com.tw</t>
+  </si>
+  <si>
+    <t>11346086@ntub.edu.tw</t>
+  </si>
+  <si>
+    <t>tammy940203@gmail.com</t>
+  </si>
+  <si>
+    <t>rose10140912@gmail.com</t>
+  </si>
+  <si>
+    <t>11344027@ntub.edu.tw</t>
+  </si>
+  <si>
+    <t>kof110165@yahoo.com.tw</t>
+  </si>
+  <si>
+    <t>11342014@ntub.edu.tw</t>
+  </si>
+  <si>
+    <t>a0936688905@gmail.com</t>
+  </si>
+  <si>
+    <t>joonni0912@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -386,9 +442,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="181" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -449,7 +505,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -788,30 +844,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB4F7476-A45A-4CCB-A819-C2977DAA9E5F}">
   <dimension ref="A1:E21"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.5" customWidth="1"/>
-    <col min="4" max="4" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" t="s">
         <v>61</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>62</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>63</v>
       </c>
-      <c r="D1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>0</v>
@@ -820,333 +876,333 @@
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="E2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="E3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="1" t="s">
+      <c r="E6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="B7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E7" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E8" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="E6" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="1" t="s">
+      <c r="E9" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E7" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="E8" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E9" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" s="1" t="s">
+      <c r="E10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="B11" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="E10" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="1" t="s">
+      <c r="E11" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="B12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="E11" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="1" t="s">
+      <c r="E12" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="B13" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E12" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+      <c r="E13" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B14" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C14" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="E13" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C14" s="1" t="s">
+      <c r="D14" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E14" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="E14" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+      <c r="B15" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="C15" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="D15" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E15" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E15" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+      <c r="B16" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="C16" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="D16" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E16" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="E16" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+      <c r="B17" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="C17" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="D17" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E17" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D17" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E17" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
+      <c r="B18" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="C18" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="D18" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E18" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="B19" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E18" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
+      <c r="E19" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B20" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C20" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D20" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E19" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
+      <c r="E20" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B21" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C21" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D20" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E20" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="D21" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E21" t="s">
-        <v>2</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
